--- a/datasets/day1_excel_foundations/homework/homework_start.xlsx
+++ b/datasets/day1_excel_foundations/homework/homework_start.xlsx
@@ -481,12 +481,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -517,12 +517,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -553,12 +553,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -589,12 +589,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -625,12 +625,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -697,12 +697,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -733,12 +733,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>David Davis</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -841,12 +841,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1057,12 +1057,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1093,12 +1093,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>John Smith</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Priya Singh</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1381,12 +1381,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Maria Garcia</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>David Davis</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wei Wang</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1633,12 +1633,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Priya Singh</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1705,12 +1705,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Priya Singh</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
